--- a/config/saveAddress.xlsx
+++ b/config/saveAddress.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,22 +482,37 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
+          <t>States (Coils)</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
           <t>INPUT BIT NO</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>MODBUS ADDRESS (Input Bits)</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>States (Input Bits)</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>PLC ANALOG INPUT SLOT</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>MODBUS ADDRESS (Analog Inputs)</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Values</t>
         </is>
       </c>
     </row>
@@ -512,25 +527,34 @@
           <t>00001</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>INPUT BIT1</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>10001</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>ANALOG INPUT1</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>30001</t>
-        </is>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>30002</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -541,28 +565,160 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>00002</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
+          <t>00001</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>INPUT BIT2</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>10002</t>
-        </is>
-      </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>10001</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>ANALOG INPUT2</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>30002</t>
-        </is>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>30003</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>OUTPUT3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>00001</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>INPUT BIT3</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>10001</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ANALOG INPUT3</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>30004</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>OUTPUT4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>00001</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>INPUT BIT4</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>10001</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ANALOG INPUT4</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>30005</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>OUTPUT5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>00001</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>INPUT BIT5</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>10001</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ANALOG INPUT5</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>30006</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -667,55 +823,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
-  <cols>
-    <col width="12.5546875" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="27.21875" bestFit="1" customWidth="1" min="5" max="5"/>
-  </cols>
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>PLC OUTPUT NO</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>MODBUS ADDRESS (Coils)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>States (Coils)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>INPUT BIT NO</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>MODBUS ADDRESS (Input Bits)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>States (Input Bits)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>PLC ANALOG INPUT SLOT</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>MODBUS ADDRESS (Analog Inputs)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Values</t>
         </is>
@@ -753,13 +905,13 @@
           <t>ANALOG INPUT1</t>
         </is>
       </c>
-      <c r="H2" t="n">
-        <v>30001</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>30001</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -770,7 +922,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>00035</t>
+          <t>00002</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -781,8 +933,10 @@
           <t>INPUT BIT2</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>10035</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>10001</t>
+        </is>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -792,13 +946,13 @@
           <t>ANALOG INPUT2</t>
         </is>
       </c>
-      <c r="H3" t="n">
-        <v>30035</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>30002</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -809,7 +963,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>00045</t>
+          <t>00003</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -820,8 +974,10 @@
           <t>INPUT BIT3</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>10045</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>10003</t>
+        </is>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -831,13 +987,13 @@
           <t>ANALOG INPUT3</t>
         </is>
       </c>
-      <c r="H4" t="n">
-        <v>30045</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>30003</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -848,7 +1004,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>00098</t>
+          <t>00004</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -859,8 +1015,10 @@
           <t>INPUT BIT4</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>10098</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>10004</t>
+        </is>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -870,13 +1028,13 @@
           <t>ANALOG INPUT4</t>
         </is>
       </c>
-      <c r="H5" t="n">
-        <v>30098</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>30004</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -887,7 +1045,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>00127</t>
+          <t>00005</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -898,8 +1056,10 @@
           <t>INPUT BIT5</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>11227</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>10005</t>
+        </is>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -909,13 +1069,218 @@
           <t>ANALOG INPUT5</t>
         </is>
       </c>
-      <c r="H6" t="n">
-        <v>30127</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>30005</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>OUTPUT6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>00006</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>INPUT BIT6</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>10006</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ANALOG INPUT6</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>30006</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>OUTPUT7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>00007</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>INPUT BIT7</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>10007</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ANALOG INPUT7</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>30007</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>OUTPUT8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>00008</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>INPUT BIT8</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>10008</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ANALOG INPUT8</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>30008</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>OUTPUT9</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>00009</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>INPUT BIT9</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>10009</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ANALOG INPUT9</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>30009</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>OUTPUT10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>00010</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>INPUT BIT10</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>10010</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ANALOG INPUT10</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>30010</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1215,9 +1580,98 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
-  <sheetData/>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>PLC OUTPUT NO</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>MODBUS ADDRESS (Coils)</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>States (Coils)</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>INPUT BIT NO</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>MODBUS ADDRESS (Input Bits)</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>States (Input Bits)</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>PLC ANALOG INPUT SLOT</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>MODBUS ADDRESS (Analog Inputs)</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Values</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>OUTPUT1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>00001</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>INPUT BIT1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>10001</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>ANALOG INPUT1</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>30001</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1228,51 +1682,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>PLC OUTPUT NO</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>MODBUS ADDRESS (Coils)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>States (Coils)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>INPUT BIT NO</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>MODBUS ADDRESS (Input Bits)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>States (Input Bits)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>PLC ANALOG INPUT SLOT</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>MODBUS ADDRESS (Analog Inputs)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Values</t>
         </is>
@@ -1310,505 +1764,13 @@
           <t>ANALOG INPUT1</t>
         </is>
       </c>
-      <c r="H2" t="n">
-        <v>30001</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>OUTPUT2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>00002</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>INPUT BIT2</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>10002</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>ANALOG INPUT2</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>30002</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>OUTPUT3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>00003</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>INPUT BIT3</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>10003</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>ANALOG INPUT3</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>30003</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>OUTPUT4</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>00004</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>INPUT BIT4</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>10004</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>ANALOG INPUT4</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>30004</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>OUTPUT5</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>00005</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>INPUT BIT5</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>10005</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>ANALOG INPUT5</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>30005</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>OUTPUT6</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>00006</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>INPUT BIT6</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>10006</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>ANALOG INPUT6</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>30006</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>OUTPUT7</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>00007</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>INPUT BIT7</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>10007</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>ANALOG INPUT7</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>30007</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>OUTPUT8</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>00008</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>INPUT BIT8</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>10008</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>ANALOG INPUT8</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>30008</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>OUTPUT9</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>00009</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>INPUT BIT9</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>10009</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>ANALOG INPUT9</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>30009</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>OUTPUT10</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>00010</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>INPUT BIT10</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>10010</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>ANALOG INPUT10</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>30010</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>OUTPUT11</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>00011</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>INPUT BIT11</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>10011</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>ANALOG INPUT11</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>30011</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>OUTPUT12</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>00012</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>INPUT BIT12</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>10012</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ANALOG INPUT12</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>30012</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>OUTPUT13</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>00013</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>INPUT BIT13</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>10013</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>ANALOG INPUT13</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>30013</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>30001</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1822,9 +1784,139 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
-  <sheetData/>
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>PLC OUTPUT NO</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>MODBUS ADDRESS (Coils)</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>States (Coils)</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>INPUT BIT NO</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>MODBUS ADDRESS (Input Bits)</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>States (Input Bits)</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>PLC ANALOG INPUT SLOT</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>MODBUS ADDRESS (Analog Inputs)</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Values</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>OUTPUT1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>00001</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>INPUT BIT1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>10001</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>ANALOG INPUT1</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>30001</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>OUTPUT2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>00030</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>INPUT BIT2</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>10040</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ANALOG INPUT2</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>30050</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1848,9 +1940,139 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
-  <sheetData/>
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>PLC OUTPUT NO</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>MODBUS ADDRESS (Coils)</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>States (Coils)</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>INPUT BIT NO</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>MODBUS ADDRESS (Input Bits)</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>States (Input Bits)</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>PLC ANALOG INPUT SLOT</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>MODBUS ADDRESS (Analog Inputs)</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Values</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>OUTPUT1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>34545</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>INPUT BIT1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>00000</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>ANALOG INPUT1</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>00000</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>OUTPUT2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>00000</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>INPUT BIT2</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>00000</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ANALOG INPUT2</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>00000</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/config/saveAddress.xlsx
+++ b/config/saveAddress.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,6 +515,21 @@
           <t>Values</t>
         </is>
       </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>HOLDING REGISTER NO</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>MODBUS ADDRESS (Holding Registers)</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>Holding Values</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -550,10 +565,23 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>30002</t>
+          <t>30001</t>
         </is>
       </c>
       <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>HOLDING REGISTER1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>40001</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -565,7 +593,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>00001</t>
+          <t>00010</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -578,7 +606,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>10001</t>
+          <t>10010</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -591,133 +619,23 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>30003</t>
+          <t>30010</t>
         </is>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>OUTPUT3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>00001</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>INPUT BIT3</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>10001</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>ANALOG INPUT3</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>30004</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>OUTPUT4</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>00001</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>INPUT BIT4</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>10001</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>ANALOG INPUT4</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>30005</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>OUTPUT5</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>00001</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>INPUT BIT5</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>10001</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>ANALOG INPUT5</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>30006</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>HOLDING REGISTER2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>40010</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1682,7 +1600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1731,6 +1649,21 @@
           <t>Values</t>
         </is>
       </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>HOLDING REGISTER NO</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>MODBUS ADDRESS (Holding Registers)</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>Holding Values</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1770,6 +1703,19 @@
         </is>
       </c>
       <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>HOLDING REGISTER1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>40001</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
         <v>0</v>
       </c>
     </row>
